--- a/apps/web/public/import-templates/players-template-va.xlsx
+++ b/apps/web/public/import-templates/players-template-va.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="jugadores" sheetId="1" r:id="rId1"/>
-    <sheet name="Guia" sheetId="2" r:id="rId2"/>
+    <sheet name="Instruccions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -17,7 +17,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
-    <t>Nom complet*</t>
+    <t>Nom*</t>
+  </si>
+  <si>
+    <t>Cognoms</t>
   </si>
   <si>
     <t>Data de naixement*</t>
@@ -29,7 +32,10 @@
     <t>Email*</t>
   </si>
   <si>
-    <t>Pepe Gómez García</t>
+    <t>Pepe</t>
+  </si>
+  <si>
+    <t>Gómez García</t>
   </si>
   <si>
     <t>15/03/2010</t>
@@ -41,7 +47,10 @@
     <t>pepe.gomez@example.com</t>
   </si>
   <si>
-    <t>Lucía Sánchez López</t>
+    <t>Lucía</t>
+  </si>
+  <si>
+    <t>Sánchez López</t>
   </si>
   <si>
     <t>03/09/2011</t>
@@ -53,7 +62,10 @@
     <t>familia.lucia@example.com</t>
   </si>
   <si>
-    <t>Mario Ruiz</t>
+    <t>Mario</t>
+  </si>
+  <si>
+    <t>Ruiz</t>
   </si>
   <si>
     <t>20/01/2012</t>
@@ -68,25 +80,28 @@
     <t>Com omplir-la</t>
   </si>
   <si>
-    <t>Nom complet</t>
-  </si>
-  <si>
-    <t>Obligatori. Nom i cognoms del jugador en una sola cel·la (ex. «Pepe Gómez García»).</t>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Obligatori. NOMÉS el nom del jugador (p. ex. "Pepe"). Els cognoms van en la seua pròpia columna.</t>
+  </si>
+  <si>
+    <t>Opcional. Els cognoms, en la seua columna (p. ex. "Gómez García"). Deixa-la buida si el jugador només té nom.</t>
   </si>
   <si>
     <t>Data de naixement</t>
   </si>
   <si>
-    <t>Obligatori. Format preferit dd/mm/yyyy (ex. 15/03/2010). També dd-mm-yyyy, yyyy-mm-dd o una cel·la Excel amb format Data.</t>
-  </si>
-  <si>
-    <t>Opcional. Nom EXACTE d’un equip existent de la temporada activa (ex. «Infantil A»). Si es deixa buit, s’usa l’equip triat en l’assistent. Un equip que no existisca dóna error (la importació no crea equips).</t>
+    <t>Obligatori. Format preferit dd/mm/aaaa (p. ex. 15/03/2010). També dd-mm-aaaa, aaaa-mm-dd o cel·la d'Excel amb format Data.</t>
+  </si>
+  <si>
+    <t>Opcional. Nom EXACTE d'un equip existent de la temporada activa (p. ex. "Infantil A"). Si es deixa buit, s'usa l'equip triat en l'assistent. Un equip que no existisca dóna error (la importació no crea equips).</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Obligatori. Correu de contacte/invitació (ex. «familia@example.com»). Serveix per a enviar la invitació després d’importar.</t>
+    <t>Obligatori. Email de contacte/invitació (p. ex. "familia@example.com"). Serveix per a enviar la invitació després d'importar.</t>
   </si>
 </sst>
 </file>
@@ -106,15 +121,27 @@
       <color theme="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBF7D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5E7EB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,9 +149,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9CA3AF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9CA3AF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9CA3AF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9CA3AF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf/>
+    <xf fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="3" applyFill="1"/>
     <xf fontId="1" applyFont="1"/>
   </cellXfs>
 </styleSheet>
@@ -137,53 +186,65 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -194,43 +255,51 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>17</v>
+      <c r="A2" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>19</v>
+      <c r="A3" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>2</v>
+      <c r="A4" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>22</v>
+      <c r="A5" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
